--- a/PTGX.xlsx
+++ b/PTGX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F080C9-CD71-4C59-9556-6EAD63B8C285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BC5624-D52B-43B9-B704-8DC19C42D29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29775" yWindow="495" windowWidth="29265" windowHeight="19335" xr2:uid="{E49AB4AD-3197-476A-9D12-79E256BF28A1}"/>
+    <workbookView xWindow="4560" yWindow="4560" windowWidth="22650" windowHeight="16100" xr2:uid="{E49AB4AD-3197-476A-9D12-79E256BF28A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
   <si>
     <t>Price</t>
   </si>
@@ -59,9 +59,6 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>Brand</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>PV</t>
   </si>
   <si>
-    <t>JNJ-2113 (icotrokinra)</t>
-  </si>
-  <si>
     <t>Administration</t>
   </si>
   <si>
@@ -326,10 +320,40 @@
     <t>Phase</t>
   </si>
   <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>JNJ</t>
+    <t>Icotyde (icotrokinra)</t>
+  </si>
+  <si>
+    <t>Approval</t>
+  </si>
+  <si>
+    <t>PN-881</t>
+  </si>
+  <si>
+    <t>IL-17R atagonist</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>PN-477sc</t>
+  </si>
+  <si>
+    <t>PN-477o</t>
+  </si>
+  <si>
+    <t>GLP/GIP/GICG agonist</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Filed</t>
+  </si>
+  <si>
+    <t>JNJ 6-10% royalty</t>
+  </si>
+  <si>
+    <t>Takeda, 14-29% royalty</t>
   </si>
 </sst>
 </file>
@@ -480,7 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -510,6 +534,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1062,35 +1089,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17C3351-904B-45B9-9BE5-F4E19BB0A4C4}">
-  <dimension ref="B2:M8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:M9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="9" width="7.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>16</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="11"/>
@@ -1098,77 +1126,98 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>95</v>
+      <c r="F3" s="21">
+        <v>46082</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I3" s="5"/>
       <c r="K3" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>58.904584999999997</v>
+        <v>65.087846999999996</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="5"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="22"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
       <c r="K4" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>2238.3742299999999</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="4"/>
+        <v>8917.0350390000003</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" t="s">
+        <v>104</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="K5" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>355.643+208.354+31.447</f>
-        <v>595.44399999999996</v>
+        <v>620</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="4"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" t="s">
+        <v>97</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="K6" t="s">
         <v>4</v>
@@ -1177,34 +1226,48 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="4"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>1642.9302299999999</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
+        <v>8297.0350390000003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" location="'JNJ-2113'!A1" display="JNJ-2113 (icotrokinra)" xr:uid="{D8F25603-18BB-4536-A573-DFBFFD603CE9}"/>
-    <hyperlink ref="B4" location="rusfertide!A1" display="rusfertide" xr:uid="{141C88F7-C588-4FE4-9EC7-EE6E3F75CCF9}"/>
+    <hyperlink ref="B5" location="rusfertide!A1" display="rusfertide" xr:uid="{141C88F7-C588-4FE4-9EC7-EE6E3F75CCF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1213,22 +1276,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07C0FEB-D0E0-45BE-9D2D-9D33993104C4}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="3"/>
-    <col min="6" max="6" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="3"/>
+    <col min="3" max="3" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.1796875" style="3"/>
+    <col min="6" max="6" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C2" s="3">
         <v>2022</v>
       </c>
@@ -1305,24 +1368,24 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>60</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="H3" s="2">
         <v>500</v>
@@ -1346,9 +1409,9 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H4" s="16">
         <v>0.1</v>
@@ -1372,9 +1435,9 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
@@ -1431,9 +1494,9 @@
         <v>514.99492454900007</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2">
         <v>50</v>
@@ -1479,9 +1542,9 @@
         <v>536.0676760535049</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="18"/>
       <c r="H7" s="2">
@@ -1533,9 +1596,9 @@
         <v>375.24737323745342</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H8" s="2">
         <f>+H7*0.5</f>
@@ -1586,9 +1649,9 @@
         <v>187.62368661872671</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2">
         <f>+G14*$C$18</f>
@@ -1639,9 +1702,9 @@
         <v>217.84130692430512</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2">
         <f>+H5+H8+H9</f>
@@ -1692,9 +1755,9 @@
         <v>920.45991809203201</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2">
         <f>+H10*0.2</f>
@@ -1745,9 +1808,9 @@
         <v>184.0919836184064</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3">
         <v>-100</v>
@@ -1804,7 +1867,7 @@
         <v>736.36793447362561</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1818,9 +1881,9 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" s="3">
         <v>595</v>
@@ -1882,38 +1945,38 @@
         <v>6182.4006075812531</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" s="20">
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="20">
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="18">
         <f>NPV(C19,F12:S12)+E14</f>
         <v>2937.652461073525</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" s="17">
         <f>C20/Main!L3</f>
-        <v>49.871371830792548</v>
+        <v>45.133655459113974</v>
       </c>
     </row>
   </sheetData>
@@ -1927,51 +1990,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CBF7A3-7E97-4630-BCA7-8686A182D672}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1985,271 +2048,271 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B35B9E-1E64-4355-9C41-8C295688A3F8}">
   <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C13" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="C17" s="15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="C18" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C16" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C17" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="13" t="s">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="C23" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" ht="13" x14ac:dyDescent="0.3">
+      <c r="C31" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C23" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C25" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C31" s="13" t="s">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C33" s="15" t="s">
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C34" t="s">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C35" t="s">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C36" t="s">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
+    <row r="39" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C39" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C42" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C45" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C48" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C51" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C53" s="14" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C45" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C48" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C51" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C53" s="14" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
